--- a/12603423.xlsx
+++ b/12603423.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c73cdbbdc1b295c5/Desktop/excel for python/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="197" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A90D0EA6-1C20-47BC-9B9E-8FD6DE5DA23B}"/>
+  <xr:revisionPtr revIDLastSave="222" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7ACF5C07-4F39-4C3E-BCF5-5D04C848C770}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
     <sheet name="Daily Log" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4" calcCompleted="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,8 +34,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -208,19 +230,10 @@
     <t>AUGUST</t>
   </si>
   <si>
-    <t>Unsatisfied</t>
-  </si>
-  <si>
-    <t>Had a productive day but felt a little tired.</t>
-  </si>
-  <si>
     <t>Neutral</t>
   </si>
   <si>
     <t>High</t>
-  </si>
-  <si>
-    <t>Attended all my classes and completed my study tasks.</t>
   </si>
   <si>
     <t>Excellent</t>
@@ -229,73 +242,40 @@
     <t>Very Satisfied</t>
   </si>
   <si>
-    <t>Spent some time coding and practiced new concepts.</t>
-  </si>
-  <si>
-    <t>I need some extra time for other activities</t>
-  </si>
-  <si>
     <t>Low</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Watching movies </t>
   </si>
   <si>
     <t>low</t>
   </si>
   <si>
-    <t xml:space="preserve">scrolling reels </t>
-  </si>
-  <si>
-    <t xml:space="preserve">low </t>
-  </si>
-  <si>
     <t>satisfied</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preaparing for networking ca </t>
   </si>
   <si>
     <t>high</t>
   </si>
   <si>
-    <t>Prepare for my ca in DBMS</t>
-  </si>
-  <si>
-    <t>revise  prevoius topic in c++</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bad </t>
-  </si>
-  <si>
-    <t xml:space="preserve">not satisfied </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suffering From Fever </t>
-  </si>
-  <si>
     <t>good</t>
   </si>
   <si>
-    <t xml:space="preserve">satisfied </t>
+    <t>Busy day with classes.</t>
   </si>
   <si>
-    <t xml:space="preserve">learning python </t>
+    <t>Good productive day.</t>
   </si>
   <si>
-    <t xml:space="preserve">good </t>
+    <t>Focused on classes and activities</t>
   </si>
   <si>
-    <t>preaparing for English Presentation.</t>
+    <t>good day</t>
   </si>
   <si>
-    <t xml:space="preserve">Busy in somework </t>
+    <t>Over all good day</t>
   </si>
   <si>
-    <t>staisfied</t>
+    <t>learn new things</t>
   </si>
   <si>
-    <t xml:space="preserve">learning python from youtube </t>
+    <t>Good day</t>
   </si>
 </sst>
 </file>
@@ -1082,9 +1062,7 @@
       </c>
     </row>
     <row r="6" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="8">
-        <v>46223</v>
-      </c>
+      <c r="A6" s="8"/>
       <c r="B6" s="9">
         <v>420</v>
       </c>
@@ -1127,205 +1105,197 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="13">
-        <v>46235</v>
+        <v>46252</v>
       </c>
       <c r="B7" s="14">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="C7" s="14">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D7" s="14">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="E7" s="14">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="F7" s="14">
-        <v>480</v>
+        <v>540</v>
       </c>
       <c r="G7" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H7" s="14">
-        <v>120</v>
+        <v>195</v>
       </c>
       <c r="I7" s="15">
-        <f t="shared" si="0"/>
-        <v>1300</v>
+        <v>1425</v>
       </c>
       <c r="J7" s="15">
-        <f t="shared" si="1"/>
-        <v>140</v>
+        <v>15</v>
       </c>
       <c r="K7" s="16" t="s">
         <v>49</v>
       </c>
       <c r="L7" s="16" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="M7" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N7" s="17" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="13">
-        <v>46236</v>
+        <v>46253</v>
       </c>
       <c r="B8" s="14">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="C8" s="14">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D8" s="14">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="E8" s="14">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="F8" s="14">
-        <v>480</v>
+        <v>240</v>
       </c>
       <c r="G8" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H8" s="14">
-        <v>140</v>
+        <v>300</v>
       </c>
       <c r="I8" s="15">
-        <f t="shared" si="0"/>
-        <v>1370</v>
+        <v>1440</v>
       </c>
       <c r="J8" s="15">
-        <f t="shared" si="1"/>
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="K8" s="16" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="L8" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M8" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N8" s="18" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" s="13">
+        <v>46254</v>
+      </c>
+      <c r="B9" s="14">
+        <v>450</v>
+      </c>
+      <c r="C9" s="14">
+        <v>20</v>
+      </c>
+      <c r="D9" s="14">
+        <v>280</v>
+      </c>
+      <c r="E9" s="14">
+        <v>90</v>
+      </c>
+      <c r="F9" s="14">
+        <v>300</v>
+      </c>
+      <c r="G9" s="14">
+        <v>6</v>
+      </c>
+      <c r="H9" s="14">
+        <v>300</v>
+      </c>
+      <c r="I9" s="15">
+        <v>1440</v>
+      </c>
+      <c r="J9" s="15">
+        <v>0</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L9" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="N8" s="18" t="s">
+      <c r="M9" s="16" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="13">
-        <v>46237</v>
-      </c>
-      <c r="B9" s="14">
+      <c r="N9" s="17" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" s="13">
+        <v>46255</v>
+      </c>
+      <c r="B10" s="14">
+        <v>430</v>
+      </c>
+      <c r="C10" s="14">
+        <v>20</v>
+      </c>
+      <c r="D10" s="14">
+        <v>140</v>
+      </c>
+      <c r="E10" s="14">
+        <v>140</v>
+      </c>
+      <c r="F10" s="14">
         <v>400</v>
-      </c>
-      <c r="C9" s="14">
-        <v>80</v>
-      </c>
-      <c r="D9" s="14">
-        <v>250</v>
-      </c>
-      <c r="E9" s="14">
-        <v>40</v>
-      </c>
-      <c r="F9" s="14">
-        <v>480</v>
-      </c>
-      <c r="G9" s="14">
-        <v>7</v>
-      </c>
-      <c r="H9" s="14">
-        <v>150</v>
-      </c>
-      <c r="I9" s="15">
-        <f t="shared" si="0"/>
-        <v>1400</v>
-      </c>
-      <c r="J9" s="15">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="K9" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="L9" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="M9" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="N9" s="17" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="13">
-        <v>46238</v>
-      </c>
-      <c r="B10" s="14">
-        <v>480</v>
-      </c>
-      <c r="C10" s="14">
-        <v>70</v>
-      </c>
-      <c r="D10" s="14">
-        <v>100</v>
-      </c>
-      <c r="E10" s="14">
-        <v>80</v>
-      </c>
-      <c r="F10" s="14">
-        <v>480</v>
       </c>
       <c r="G10" s="14">
         <v>7</v>
       </c>
       <c r="H10" s="14">
-        <v>200</v>
+        <v>310</v>
       </c>
       <c r="I10" s="15">
-        <f t="shared" si="0"/>
-        <v>1410</v>
+        <v>1440</v>
       </c>
       <c r="J10" s="15">
-        <f t="shared" si="1"/>
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K10" s="16" t="s">
         <v>49</v>
       </c>
       <c r="L10" s="16" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="M10" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="13">
-        <v>46239</v>
+        <v>46256</v>
       </c>
       <c r="B11" s="14">
         <v>460</v>
       </c>
       <c r="C11" s="14">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D11" s="14">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E11" s="14">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="F11" s="14">
         <v>0</v>
@@ -1334,44 +1304,42 @@
         <v>0</v>
       </c>
       <c r="H11" s="14">
-        <v>120</v>
+        <v>490</v>
       </c>
       <c r="I11" s="15">
-        <f t="shared" si="0"/>
-        <v>780</v>
+        <v>1440</v>
       </c>
       <c r="J11" s="15">
-        <f t="shared" si="1"/>
-        <v>660</v>
+        <v>0</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="L11" s="16" t="s">
         <v>57</v>
       </c>
       <c r="M11" s="16" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="13">
-        <v>46240</v>
+        <v>46257</v>
       </c>
       <c r="B12" s="14">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="C12" s="14">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D12" s="14">
-        <v>100</v>
+        <v>360</v>
       </c>
       <c r="E12" s="14">
-        <v>40</v>
+        <v>180</v>
       </c>
       <c r="F12" s="14">
         <v>0</v>
@@ -1380,110 +1348,104 @@
         <v>0</v>
       </c>
       <c r="H12" s="14">
-        <v>130</v>
+        <v>410</v>
       </c>
       <c r="I12" s="15">
-        <f t="shared" si="0"/>
-        <v>820</v>
+        <v>1440</v>
       </c>
       <c r="J12" s="15">
-        <f t="shared" si="1"/>
-        <v>620</v>
+        <v>0</v>
       </c>
       <c r="K12" s="16" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="L12" s="16" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M12" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="13">
-        <v>46241</v>
+        <v>46258</v>
       </c>
       <c r="B13" s="14">
-        <v>500</v>
+        <v>420</v>
       </c>
       <c r="C13" s="14">
+        <v>20</v>
+      </c>
+      <c r="D13" s="14">
+        <v>420</v>
+      </c>
+      <c r="E13" s="14">
+        <v>140</v>
+      </c>
+      <c r="F13" s="14">
         <v>100</v>
       </c>
-      <c r="D13" s="14">
-        <v>90</v>
-      </c>
-      <c r="E13" s="14">
-        <v>30</v>
-      </c>
-      <c r="F13" s="14">
-        <v>480</v>
-      </c>
       <c r="G13" s="14">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H13" s="14">
-        <v>120</v>
+        <v>330</v>
       </c>
       <c r="I13" s="15">
-        <f t="shared" si="0"/>
-        <v>1320</v>
+        <v>1430</v>
       </c>
       <c r="J13" s="15">
-        <f t="shared" si="1"/>
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="K13" s="16" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="L13" s="16" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="M13" s="16" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="13">
-        <v>46242</v>
+        <v>46259</v>
       </c>
       <c r="B14" s="14">
-        <v>500</v>
+        <v>440</v>
       </c>
       <c r="C14" s="14">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D14" s="14">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="E14" s="14">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="F14" s="14">
-        <v>480</v>
+        <v>350</v>
       </c>
       <c r="G14" s="14">
         <v>7</v>
       </c>
       <c r="H14" s="14">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="I14" s="15">
-        <f t="shared" si="0"/>
-        <v>1260</v>
+        <v>1360</v>
       </c>
       <c r="J14" s="15">
-        <f t="shared" si="1"/>
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="L14" s="16" t="s">
         <v>50</v>
@@ -1492,284 +1454,245 @@
         <v>51</v>
       </c>
       <c r="N14" s="17" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13">
-        <v>46243</v>
+      <c r="A15" s="13" cm="1">
+        <f t="array" aca="1" ref="A15" ca="1">A15:N5126-8-2026</f>
+        <v>0</v>
       </c>
       <c r="B15" s="14">
-        <v>480</v>
+        <v>420</v>
       </c>
       <c r="C15" s="14">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
+        <v>180</v>
+      </c>
+      <c r="E15" s="14">
         <v>60</v>
       </c>
-      <c r="D15" s="14">
-        <v>90</v>
-      </c>
-      <c r="E15" s="14">
-        <v>50</v>
-      </c>
       <c r="F15" s="14">
-        <v>480</v>
+        <v>200</v>
       </c>
       <c r="G15" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H15" s="14">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="I15" s="15">
-        <f t="shared" si="0"/>
-        <v>1280</v>
+        <v>1180</v>
       </c>
       <c r="J15" s="15">
-        <f t="shared" si="1"/>
-        <v>160</v>
+        <v>260</v>
       </c>
       <c r="K15" s="16" t="s">
         <v>49</v>
       </c>
       <c r="L15" s="16" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="M15" s="16" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="N15" s="17" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="13">
-        <v>46244</v>
+        <v>46261</v>
       </c>
       <c r="B16" s="14">
-        <v>600</v>
+        <v>440</v>
       </c>
       <c r="C16" s="14">
         <v>20</v>
       </c>
       <c r="D16" s="14">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="E16" s="14">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="F16" s="14">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="G16" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H16" s="14">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="I16" s="15">
-        <f t="shared" si="0"/>
-        <v>1060</v>
+        <v>1250</v>
       </c>
       <c r="J16" s="15">
-        <f t="shared" si="1"/>
-        <v>380</v>
+        <v>190</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="M16" s="16" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>78</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="13">
-        <v>46245</v>
+        <v>46262</v>
       </c>
       <c r="B17" s="14">
-        <v>500</v>
+        <v>420</v>
       </c>
       <c r="C17" s="14">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D17" s="14">
-        <v>30</v>
+        <v>130</v>
       </c>
       <c r="E17" s="14">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="F17" s="14">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="G17" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H17" s="14">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="I17" s="15">
-        <f t="shared" si="0"/>
-        <v>1090</v>
+        <v>1280</v>
       </c>
       <c r="J17" s="15">
-        <f t="shared" si="1"/>
-        <v>350</v>
+        <v>160</v>
       </c>
       <c r="K17" s="16" t="s">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="M17" s="16" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="13">
-        <v>46245</v>
+        <v>46263</v>
       </c>
       <c r="B18" s="14">
-        <v>480</v>
+        <v>460</v>
       </c>
       <c r="C18" s="14">
+        <v>20</v>
+      </c>
+      <c r="D18" s="14">
+        <v>250</v>
+      </c>
+      <c r="E18" s="14">
+        <v>210</v>
+      </c>
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14">
+        <v>253</v>
+      </c>
+      <c r="I18" s="15">
+        <v>1193</v>
+      </c>
+      <c r="J18" s="15">
+        <v>247</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L18" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="D18" s="14">
-        <v>70</v>
-      </c>
-      <c r="E18" s="14">
-        <v>80</v>
-      </c>
-      <c r="F18" s="14">
-        <v>480</v>
-      </c>
-      <c r="G18" s="14">
-        <v>7</v>
-      </c>
-      <c r="H18" s="14">
-        <v>120</v>
-      </c>
-      <c r="I18" s="15">
-        <f t="shared" si="0"/>
-        <v>1290</v>
-      </c>
-      <c r="J18" s="15">
-        <f t="shared" si="1"/>
-        <v>150</v>
-      </c>
-      <c r="K18" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="L18" s="16" t="s">
-        <v>71</v>
-      </c>
       <c r="M18" s="16" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="13">
-        <v>46246</v>
+        <v>46264</v>
       </c>
       <c r="B19" s="14">
-        <v>500</v>
+        <v>460</v>
       </c>
       <c r="C19" s="14">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="D19" s="14">
-        <v>50</v>
+        <v>230</v>
       </c>
       <c r="E19" s="14">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="F19" s="14">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G19" s="14">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H19" s="14">
-        <v>70</v>
+        <v>310</v>
       </c>
       <c r="I19" s="15">
-        <f t="shared" si="0"/>
-        <v>1140</v>
+        <v>1200</v>
       </c>
       <c r="J19" s="15">
-        <f t="shared" si="1"/>
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="K19" s="16" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="M19" s="16" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13">
-        <v>46247</v>
-      </c>
-      <c r="B20" s="14">
-        <v>480</v>
-      </c>
-      <c r="C20" s="14">
-        <v>80</v>
-      </c>
-      <c r="D20" s="14">
-        <v>80</v>
-      </c>
-      <c r="E20" s="14">
-        <v>20</v>
-      </c>
-      <c r="F20" s="14">
-        <v>480</v>
-      </c>
-      <c r="G20" s="14">
-        <v>7</v>
-      </c>
-      <c r="H20" s="14">
-        <v>80</v>
-      </c>
-      <c r="I20" s="15">
-        <f t="shared" si="0"/>
-        <v>1220</v>
-      </c>
-      <c r="J20" s="15">
-        <f t="shared" si="1"/>
-        <v>220</v>
-      </c>
-      <c r="K20" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="L20" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="M20" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="N20" s="17" t="s">
-        <v>86</v>
-      </c>
+      <c r="A20" s="13"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="16"/>
+      <c r="L20" s="16"/>
+      <c r="M20" s="16"/>
+      <c r="N20" s="17"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>
@@ -1780,14 +1703,8 @@
       <c r="F21" s="14"/>
       <c r="G21" s="14"/>
       <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
       <c r="K21" s="16"/>
       <c r="L21" s="16"/>
       <c r="M21" s="16"/>
@@ -1802,14 +1719,8 @@
       <c r="F22" s="14"/>
       <c r="G22" s="14"/>
       <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
       <c r="K22" s="16"/>
       <c r="L22" s="16"/>
       <c r="M22" s="16"/>
@@ -1824,14 +1735,8 @@
       <c r="F23" s="14"/>
       <c r="G23" s="14"/>
       <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I23" s="15"/>
+      <c r="J23" s="15"/>
       <c r="K23" s="16"/>
       <c r="L23" s="16"/>
       <c r="M23" s="16"/>
@@ -1846,14 +1751,8 @@
       <c r="F24" s="14"/>
       <c r="G24" s="14"/>
       <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I24" s="15"/>
+      <c r="J24" s="15"/>
       <c r="K24" s="16"/>
       <c r="L24" s="16"/>
       <c r="M24" s="16"/>
@@ -1868,14 +1767,8 @@
       <c r="F25" s="14"/>
       <c r="G25" s="14"/>
       <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I25" s="15"/>
+      <c r="J25" s="15"/>
       <c r="K25" s="16"/>
       <c r="L25" s="16"/>
       <c r="M25" s="16"/>
@@ -1890,14 +1783,8 @@
       <c r="F26" s="14"/>
       <c r="G26" s="14"/>
       <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I26" s="15"/>
+      <c r="J26" s="15"/>
       <c r="K26" s="16"/>
       <c r="L26" s="16"/>
       <c r="M26" s="16"/>
@@ -1912,14 +1799,8 @@
       <c r="F27" s="14"/>
       <c r="G27" s="14"/>
       <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I27" s="15"/>
+      <c r="J27" s="15"/>
       <c r="K27" s="16"/>
       <c r="L27" s="16"/>
       <c r="M27" s="16"/>
@@ -1934,14 +1815,8 @@
       <c r="F28" s="14"/>
       <c r="G28" s="14"/>
       <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I28" s="15"/>
+      <c r="J28" s="15"/>
       <c r="K28" s="16"/>
       <c r="L28" s="16"/>
       <c r="M28" s="16"/>
@@ -1956,14 +1831,8 @@
       <c r="F29" s="14"/>
       <c r="G29" s="14"/>
       <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I29" s="15"/>
+      <c r="J29" s="15"/>
       <c r="K29" s="16"/>
       <c r="L29" s="16"/>
       <c r="M29" s="16"/>
@@ -1978,14 +1847,8 @@
       <c r="F30" s="14"/>
       <c r="G30" s="14"/>
       <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I30" s="15"/>
+      <c r="J30" s="15"/>
       <c r="K30" s="16"/>
       <c r="L30" s="16"/>
       <c r="M30" s="16"/>
@@ -2000,14 +1863,8 @@
       <c r="F31" s="14"/>
       <c r="G31" s="14"/>
       <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I31" s="15"/>
+      <c r="J31" s="15"/>
       <c r="K31" s="16"/>
       <c r="L31" s="16"/>
       <c r="M31" s="16"/>
@@ -2022,14 +1879,8 @@
       <c r="F32" s="14"/>
       <c r="G32" s="14"/>
       <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I32" s="15"/>
+      <c r="J32" s="15"/>
       <c r="K32" s="16"/>
       <c r="L32" s="16"/>
       <c r="M32" s="16"/>
@@ -2044,14 +1895,8 @@
       <c r="F33" s="14"/>
       <c r="G33" s="14"/>
       <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I33" s="15"/>
+      <c r="J33" s="15"/>
       <c r="K33" s="16"/>
       <c r="L33" s="16"/>
       <c r="M33" s="16"/>
@@ -2066,14 +1911,8 @@
       <c r="F34" s="14"/>
       <c r="G34" s="14"/>
       <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I34" s="15"/>
+      <c r="J34" s="15"/>
       <c r="K34" s="16"/>
       <c r="L34" s="16"/>
       <c r="M34" s="16"/>
@@ -2088,14 +1927,8 @@
       <c r="F35" s="14"/>
       <c r="G35" s="14"/>
       <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I35" s="15"/>
+      <c r="J35" s="15"/>
       <c r="K35" s="16"/>
       <c r="L35" s="16"/>
       <c r="M35" s="16"/>
@@ -2110,14 +1943,8 @@
       <c r="F36" s="14"/>
       <c r="G36" s="14"/>
       <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I36" s="15"/>
+      <c r="J36" s="15"/>
       <c r="K36" s="16"/>
       <c r="L36" s="16"/>
       <c r="M36" s="16"/>
@@ -2132,14 +1959,8 @@
       <c r="F37" s="14"/>
       <c r="G37" s="14"/>
       <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I37" s="15"/>
+      <c r="J37" s="15"/>
       <c r="K37" s="16"/>
       <c r="L37" s="16"/>
       <c r="M37" s="16"/>
@@ -2154,14 +1975,8 @@
       <c r="F38" s="14"/>
       <c r="G38" s="14"/>
       <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I38" s="15"/>
+      <c r="J38" s="15"/>
       <c r="K38" s="16"/>
       <c r="L38" s="16"/>
       <c r="M38" s="16"/>
@@ -2176,14 +1991,8 @@
       <c r="F39" s="14"/>
       <c r="G39" s="14"/>
       <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I39" s="15"/>
+      <c r="J39" s="15"/>
       <c r="K39" s="16"/>
       <c r="L39" s="16"/>
       <c r="M39" s="16"/>
@@ -2198,14 +2007,8 @@
       <c r="F40" s="14"/>
       <c r="G40" s="14"/>
       <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I40" s="15"/>
+      <c r="J40" s="15"/>
       <c r="K40" s="16"/>
       <c r="L40" s="16"/>
       <c r="M40" s="16"/>
@@ -2220,14 +2023,8 @@
       <c r="F41" s="14"/>
       <c r="G41" s="14"/>
       <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I41" s="15"/>
+      <c r="J41" s="15"/>
       <c r="K41" s="16"/>
       <c r="L41" s="16"/>
       <c r="M41" s="16"/>
@@ -2242,14 +2039,8 @@
       <c r="F42" s="14"/>
       <c r="G42" s="14"/>
       <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I42" s="15"/>
+      <c r="J42" s="15"/>
       <c r="K42" s="16"/>
       <c r="L42" s="16"/>
       <c r="M42" s="16"/>
@@ -2264,14 +2055,8 @@
       <c r="F43" s="14"/>
       <c r="G43" s="14"/>
       <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I43" s="15"/>
+      <c r="J43" s="15"/>
       <c r="K43" s="16"/>
       <c r="L43" s="16"/>
       <c r="M43" s="16"/>
@@ -2286,14 +2071,8 @@
       <c r="F44" s="14"/>
       <c r="G44" s="14"/>
       <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I44" s="15"/>
+      <c r="J44" s="15"/>
       <c r="K44" s="16"/>
       <c r="L44" s="16"/>
       <c r="M44" s="16"/>
@@ -2308,14 +2087,8 @@
       <c r="F45" s="14"/>
       <c r="G45" s="14"/>
       <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I45" s="15"/>
+      <c r="J45" s="15"/>
       <c r="K45" s="16"/>
       <c r="L45" s="16"/>
       <c r="M45" s="16"/>
@@ -2330,14 +2103,8 @@
       <c r="F46" s="14"/>
       <c r="G46" s="14"/>
       <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="I46" s="15"/>
+      <c r="J46" s="15"/>
       <c r="K46" s="16"/>
       <c r="L46" s="16"/>
       <c r="M46" s="16"/>

--- a/12603423.xlsx
+++ b/12603423.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c73cdbbdc1b295c5/Desktop/excel for python/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="222" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7ACF5C07-4F39-4C3E-BCF5-5D04C848C770}"/>
+  <xr:revisionPtr revIDLastSave="234" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{701B6447-7E9F-416E-80FB-AECC30B34371}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
     <sheet name="Daily Log" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4" calcCompleted="0"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,30 +34,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -213,9 +191,6 @@
   </si>
   <si>
     <t>Medium</t>
-  </si>
-  <si>
-    <t>Example row — replace with your own data. Felt a bit tired after evening class.</t>
   </si>
   <si>
     <t>5. GOOD PRACTICE</t>
@@ -900,7 +875,7 @@
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
@@ -970,7 +945,7 @@
         <v>30</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C2" s="21"/>
       <c r="D2" s="21"/>
@@ -987,7 +962,7 @@
         <v>32</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C3" s="21"/>
       <c r="D3" s="21"/>
@@ -995,7 +970,7 @@
         <v>33</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G3" s="21"/>
     </row>
@@ -1061,36 +1036,36 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="8"/>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" s="8">
+        <v>46252</v>
+      </c>
       <c r="B6" s="9">
         <v>420</v>
       </c>
       <c r="C6" s="9">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D6" s="9">
         <v>120</v>
       </c>
       <c r="E6" s="9">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="F6" s="9">
-        <v>180</v>
+        <v>540</v>
       </c>
       <c r="G6" s="9">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H6" s="9">
-        <v>30</v>
+        <v>195</v>
       </c>
       <c r="I6" s="10">
-        <f t="shared" ref="I6:I69" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
-        <v>885</v>
+        <v>1425</v>
       </c>
       <c r="J6" s="10">
-        <f t="shared" ref="J6:J69" si="1">IF(I6="","",1440-I6)</f>
-        <v>555</v>
+        <v>15</v>
       </c>
       <c r="K6" s="11" t="s">
         <v>49</v>
@@ -1102,12 +1077,12 @@
         <v>51</v>
       </c>
       <c r="N6" s="12" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="13">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B7" s="14">
         <v>420</v>
@@ -1116,25 +1091,25 @@
         <v>30</v>
       </c>
       <c r="D7" s="14">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="E7" s="14">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="F7" s="14">
-        <v>540</v>
+        <v>240</v>
       </c>
       <c r="G7" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H7" s="14">
-        <v>195</v>
+        <v>300</v>
       </c>
       <c r="I7" s="15">
-        <v>1425</v>
+        <v>1440</v>
       </c>
       <c r="J7" s="15">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K7" s="16" t="s">
         <v>49</v>
@@ -1143,7 +1118,7 @@
         <v>50</v>
       </c>
       <c r="M7" s="16" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="N7" s="17" t="s">
         <v>66</v>
@@ -1151,25 +1126,25 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="13">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B8" s="14">
-        <v>420</v>
+        <v>450</v>
       </c>
       <c r="C8" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D8" s="14">
+        <v>280</v>
+      </c>
+      <c r="E8" s="14">
+        <v>90</v>
+      </c>
+      <c r="F8" s="14">
         <v>300</v>
       </c>
-      <c r="E8" s="14">
-        <v>150</v>
-      </c>
-      <c r="F8" s="14">
-        <v>240</v>
-      </c>
       <c r="G8" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H8" s="14">
         <v>300</v>
@@ -1181,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="K8" s="16" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="L8" s="16" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="M8" s="16" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="N8" s="18" t="s">
         <v>67</v>
@@ -1195,28 +1170,28 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="13">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B9" s="14">
-        <v>450</v>
+        <v>430</v>
       </c>
       <c r="C9" s="14">
         <v>20</v>
       </c>
       <c r="D9" s="14">
-        <v>280</v>
+        <v>140</v>
       </c>
       <c r="E9" s="14">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="F9" s="14">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="G9" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H9" s="14">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="I9" s="15">
         <v>1440</v>
@@ -1225,13 +1200,13 @@
         <v>0</v>
       </c>
       <c r="K9" s="16" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="L9" s="16" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="M9" s="16" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="N9" s="17" t="s">
         <v>68</v>
@@ -1239,28 +1214,28 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="13">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B10" s="14">
-        <v>430</v>
+        <v>460</v>
       </c>
       <c r="C10" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D10" s="14">
-        <v>140</v>
+        <v>300</v>
       </c>
       <c r="E10" s="14">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="F10" s="14">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G10" s="14">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H10" s="14">
-        <v>310</v>
+        <v>490</v>
       </c>
       <c r="I10" s="15">
         <v>1440</v>
@@ -1269,13 +1244,13 @@
         <v>0</v>
       </c>
       <c r="K10" s="16" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="L10" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M10" s="16" t="s">
         <v>57</v>
-      </c>
-      <c r="M10" s="16" t="s">
-        <v>51</v>
       </c>
       <c r="N10" s="17" t="s">
         <v>69</v>
@@ -1283,19 +1258,19 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="13">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B11" s="14">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="C11" s="14">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D11" s="14">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="E11" s="14">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="F11" s="14">
         <v>0</v>
@@ -1304,7 +1279,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="14">
-        <v>490</v>
+        <v>410</v>
       </c>
       <c r="I11" s="15">
         <v>1440</v>
@@ -1313,286 +1288,285 @@
         <v>0</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="L11" s="16" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="M11" s="16" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="13">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B12" s="14">
-        <v>450</v>
+        <v>420</v>
       </c>
       <c r="C12" s="14">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D12" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="E12" s="14">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="F12" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G12" s="14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12" s="14">
-        <v>410</v>
+        <v>330</v>
       </c>
       <c r="I12" s="15">
-        <v>1440</v>
+        <v>1430</v>
       </c>
       <c r="J12" s="15">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K12" s="16" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L12" s="16" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="M12" s="16" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="13">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B13" s="14">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="C13" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D13" s="14">
-        <v>420</v>
+        <v>160</v>
       </c>
       <c r="E13" s="14">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="F13" s="14">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="G13" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H13" s="14">
-        <v>330</v>
+        <v>200</v>
       </c>
       <c r="I13" s="15">
-        <v>1430</v>
+        <v>1360</v>
       </c>
       <c r="J13" s="15">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="K13" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L13" s="16" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="M13" s="16" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="13">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B14" s="14">
+        <v>420</v>
+      </c>
+      <c r="C14" s="14">
+        <v>20</v>
+      </c>
+      <c r="D14" s="14">
+        <v>180</v>
+      </c>
+      <c r="E14" s="14">
+        <v>60</v>
+      </c>
+      <c r="F14" s="14">
+        <v>200</v>
+      </c>
+      <c r="G14" s="14">
+        <v>4</v>
+      </c>
+      <c r="H14" s="14">
+        <v>300</v>
+      </c>
+      <c r="I14" s="15">
+        <v>1180</v>
+      </c>
+      <c r="J14" s="15">
+        <v>260</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B15" s="14">
         <v>440</v>
-      </c>
-      <c r="C14" s="14">
-        <v>30</v>
-      </c>
-      <c r="D14" s="14">
-        <v>160</v>
-      </c>
-      <c r="E14" s="14">
-        <v>180</v>
-      </c>
-      <c r="F14" s="14">
-        <v>350</v>
-      </c>
-      <c r="G14" s="14">
-        <v>7</v>
-      </c>
-      <c r="H14" s="14">
-        <v>200</v>
-      </c>
-      <c r="I14" s="15">
-        <v>1360</v>
-      </c>
-      <c r="J14" s="15">
-        <v>80</v>
-      </c>
-      <c r="K14" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="L14" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M14" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="N14" s="17" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13" cm="1">
-        <f t="array" aca="1" ref="A15" ca="1">A15:N5126-8-2026</f>
-        <v>0</v>
-      </c>
-      <c r="B15" s="14">
-        <v>420</v>
       </c>
       <c r="C15" s="14">
         <v>20</v>
       </c>
       <c r="D15" s="14">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="E15" s="14">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="F15" s="14">
+        <v>350</v>
+      </c>
+      <c r="G15" s="14">
+        <v>7</v>
+      </c>
+      <c r="H15" s="14">
         <v>200</v>
       </c>
-      <c r="G15" s="14">
-        <v>4</v>
-      </c>
-      <c r="H15" s="14">
-        <v>300</v>
-      </c>
       <c r="I15" s="15">
-        <v>1180</v>
+        <v>1250</v>
       </c>
       <c r="J15" s="15">
-        <v>260</v>
+        <v>190</v>
       </c>
       <c r="K15" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N15" s="17" t="s">
         <v>49</v>
-      </c>
-      <c r="L15" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="M15" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="N15" s="17" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="13">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B16" s="14">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="C16" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D16" s="14">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="E16" s="14">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="F16" s="14">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="G16" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H16" s="14">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="I16" s="15">
-        <v>1250</v>
+        <v>1280</v>
       </c>
       <c r="J16" s="15">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="M16" s="16" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="13">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B17" s="14">
-        <v>420</v>
+        <v>460</v>
       </c>
       <c r="C17" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D17" s="14">
-        <v>130</v>
+        <v>250</v>
       </c>
       <c r="E17" s="14">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="F17" s="14">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G17" s="14">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H17" s="14">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="I17" s="15">
-        <v>1280</v>
+        <v>1193</v>
       </c>
       <c r="J17" s="15">
-        <v>160</v>
+        <v>247</v>
       </c>
       <c r="K17" s="16" t="s">
         <v>49</v>
       </c>
       <c r="L17" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M17" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="M17" s="16" t="s">
-        <v>62</v>
-      </c>
       <c r="N17" s="17" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="13">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B18" s="14">
         <v>460</v>
@@ -1601,10 +1575,10 @@
         <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="E18" s="14">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="F18" s="14">
         <v>0</v>
@@ -1613,86 +1587,114 @@
         <v>0</v>
       </c>
       <c r="H18" s="14">
-        <v>253</v>
+        <v>310</v>
       </c>
       <c r="I18" s="15">
-        <v>1193</v>
+        <v>1200</v>
       </c>
       <c r="J18" s="15">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="L18" s="16" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M18" s="16" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="13">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B19" s="14">
-        <v>460</v>
+        <v>420</v>
       </c>
       <c r="C19" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D19" s="14">
-        <v>230</v>
+        <v>410</v>
       </c>
       <c r="E19" s="14">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="F19" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G19" s="14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H19" s="14">
-        <v>310</v>
+        <v>375</v>
       </c>
       <c r="I19" s="15">
-        <v>1200</v>
+        <v>1435</v>
       </c>
       <c r="J19" s="15">
-        <v>240</v>
+        <v>5</v>
       </c>
       <c r="K19" s="16" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="M19" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15"/>
-      <c r="J20" s="15"/>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+      <c r="A20" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B20" s="14">
+        <v>420</v>
+      </c>
+      <c r="C20" s="14">
+        <v>40</v>
+      </c>
+      <c r="D20" s="14">
+        <v>200</v>
+      </c>
+      <c r="E20" s="14">
+        <v>120</v>
+      </c>
+      <c r="F20" s="14">
+        <v>350</v>
+      </c>
+      <c r="G20" s="14">
+        <v>7</v>
+      </c>
+      <c r="H20" s="14">
+        <v>200</v>
+      </c>
+      <c r="I20" s="15">
+        <v>1330</v>
+      </c>
+      <c r="J20" s="15">
+        <v>110</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>
@@ -2120,11 +2122,11 @@
       <c r="G47" s="14"/>
       <c r="H47" s="14"/>
       <c r="I47" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I6:I69" si="0">IF(SUM(B47:F47,H47)=0,"",SUM(B47:F47,H47))</f>
         <v/>
       </c>
       <c r="J47" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J6:J69" si="1">IF(I47="","",1440-I47)</f>
         <v/>
       </c>
       <c r="K47" s="16"/>

--- a/12603423.xlsx
+++ b/12603423.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c73cdbbdc1b295c5/Desktop/excel for python/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="234" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{701B6447-7E9F-416E-80FB-AECC30B34371}"/>
+  <xr:revisionPtr revIDLastSave="251" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{349ABAB0-2ED0-41D5-89C9-C215DED6558D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -389,7 +389,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -436,6 +436,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1081,8 +1082,8 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="13">
-        <v>46253</v>
+      <c r="A7" s="22">
+        <v>46252</v>
       </c>
       <c r="B7" s="14">
         <v>420</v>
@@ -1091,25 +1092,25 @@
         <v>30</v>
       </c>
       <c r="D7" s="14">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="E7" s="14">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="F7" s="14">
-        <v>240</v>
+        <v>540</v>
       </c>
       <c r="G7" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H7" s="14">
-        <v>300</v>
+        <v>195</v>
       </c>
       <c r="I7" s="15">
-        <v>1440</v>
+        <v>1425</v>
       </c>
       <c r="J7" s="15">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K7" s="16" t="s">
         <v>49</v>
@@ -1118,33 +1119,33 @@
         <v>50</v>
       </c>
       <c r="M7" s="16" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="N7" s="17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="13">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="B8" s="14">
-        <v>450</v>
+        <v>420</v>
       </c>
       <c r="C8" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D8" s="14">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="E8" s="14">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="F8" s="14">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="G8" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H8" s="14">
         <v>300</v>
@@ -1156,42 +1157,42 @@
         <v>0</v>
       </c>
       <c r="K8" s="16" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="L8" s="16" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="M8" s="16" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="N8" s="18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="13">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="B9" s="14">
-        <v>430</v>
+        <v>450</v>
       </c>
       <c r="C9" s="14">
         <v>20</v>
       </c>
       <c r="D9" s="14">
-        <v>140</v>
+        <v>280</v>
       </c>
       <c r="E9" s="14">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="F9" s="14">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G9" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H9" s="14">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="I9" s="15">
         <v>1440</v>
@@ -1200,42 +1201,42 @@
         <v>0</v>
       </c>
       <c r="K9" s="16" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="L9" s="16" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="M9" s="16" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="13">
-        <v>46256</v>
+        <v>46255</v>
       </c>
       <c r="B10" s="14">
-        <v>460</v>
+        <v>430</v>
       </c>
       <c r="C10" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D10" s="14">
-        <v>300</v>
+        <v>140</v>
       </c>
       <c r="E10" s="14">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="F10" s="14">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="G10" s="14">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H10" s="14">
-        <v>490</v>
+        <v>310</v>
       </c>
       <c r="I10" s="15">
         <v>1440</v>
@@ -1244,33 +1245,33 @@
         <v>0</v>
       </c>
       <c r="K10" s="16" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="L10" s="16" t="s">
         <v>56</v>
       </c>
       <c r="M10" s="16" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="13">
-        <v>46257</v>
+        <v>46256</v>
       </c>
       <c r="B11" s="14">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="C11" s="14">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D11" s="14">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="E11" s="14">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="F11" s="14">
         <v>0</v>
@@ -1279,7 +1280,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="14">
-        <v>410</v>
+        <v>490</v>
       </c>
       <c r="I11" s="15">
         <v>1440</v>
@@ -1288,285 +1289,285 @@
         <v>0</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L11" s="16" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="M11" s="16" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="13">
-        <v>46258</v>
+        <v>46257</v>
       </c>
       <c r="B12" s="14">
-        <v>420</v>
+        <v>450</v>
       </c>
       <c r="C12" s="14">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D12" s="14">
-        <v>420</v>
+        <v>360</v>
       </c>
       <c r="E12" s="14">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="F12" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G12" s="14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H12" s="14">
-        <v>330</v>
+        <v>410</v>
       </c>
       <c r="I12" s="15">
-        <v>1430</v>
+        <v>1440</v>
       </c>
       <c r="J12" s="15">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K12" s="16" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="L12" s="16" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="M12" s="16" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="13">
-        <v>46259</v>
+        <v>46258</v>
       </c>
       <c r="B13" s="14">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="C13" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D13" s="14">
-        <v>160</v>
+        <v>420</v>
       </c>
       <c r="E13" s="14">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="F13" s="14">
-        <v>350</v>
+        <v>100</v>
       </c>
       <c r="G13" s="14">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H13" s="14">
-        <v>200</v>
+        <v>330</v>
       </c>
       <c r="I13" s="15">
-        <v>1360</v>
+        <v>1430</v>
       </c>
       <c r="J13" s="15">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="K13" s="16" t="s">
         <v>56</v>
       </c>
       <c r="L13" s="16" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="M13" s="16" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="13">
-        <v>46260</v>
+        <v>46259</v>
       </c>
       <c r="B14" s="14">
-        <v>420</v>
-      </c>
-      <c r="C14" s="14">
-        <v>20</v>
+        <v>440</v>
+      </c>
+      <c r="C14" s="13">
+        <v>30</v>
       </c>
       <c r="D14" s="14">
+        <v>160</v>
+      </c>
+      <c r="E14" s="14">
         <v>180</v>
       </c>
-      <c r="E14" s="14">
-        <v>60</v>
-      </c>
       <c r="F14" s="14">
+        <v>350</v>
+      </c>
+      <c r="G14" s="14">
+        <v>7</v>
+      </c>
+      <c r="H14" s="14">
         <v>200</v>
       </c>
-      <c r="G14" s="14">
-        <v>4</v>
-      </c>
-      <c r="H14" s="14">
-        <v>300</v>
-      </c>
       <c r="I14" s="15">
-        <v>1180</v>
+        <v>1360</v>
       </c>
       <c r="J14" s="15">
-        <v>260</v>
+        <v>80</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="L14" s="16" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="M14" s="16" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="N14" s="17" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="13">
-        <v>46261</v>
+        <v>46260</v>
       </c>
       <c r="B15" s="14">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="C15" s="14">
         <v>20</v>
       </c>
       <c r="D15" s="14">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="E15" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="F15" s="14">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="G15" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H15" s="14">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I15" s="15">
-        <v>1250</v>
+        <v>1180</v>
       </c>
       <c r="J15" s="15">
-        <v>190</v>
+        <v>260</v>
       </c>
       <c r="K15" s="16" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="L15" s="16" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="M15" s="16" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="N15" s="17" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="13">
-        <v>46262</v>
+        <v>46261</v>
       </c>
       <c r="B16" s="14">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="C16" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D16" s="14">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="E16" s="14">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="F16" s="14">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="G16" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H16" s="14">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="I16" s="15">
-        <v>1280</v>
+        <v>1250</v>
       </c>
       <c r="J16" s="15">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="K16" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N16" s="17" t="s">
         <v>49</v>
-      </c>
-      <c r="L16" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="M16" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="N16" s="17" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="13">
-        <v>46263</v>
+        <v>46262</v>
       </c>
       <c r="B17" s="14">
-        <v>460</v>
+        <v>420</v>
       </c>
       <c r="C17" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D17" s="14">
+        <v>130</v>
+      </c>
+      <c r="E17" s="14">
+        <v>150</v>
+      </c>
+      <c r="F17" s="14">
+        <v>300</v>
+      </c>
+      <c r="G17" s="14">
+        <v>6</v>
+      </c>
+      <c r="H17" s="14">
         <v>250</v>
       </c>
-      <c r="E17" s="14">
-        <v>210</v>
-      </c>
-      <c r="F17" s="14">
-        <v>0</v>
-      </c>
-      <c r="G17" s="14">
-        <v>0</v>
-      </c>
-      <c r="H17" s="14">
-        <v>253</v>
-      </c>
       <c r="I17" s="15">
-        <v>1193</v>
+        <v>1280</v>
       </c>
       <c r="J17" s="15">
-        <v>247</v>
+        <v>160</v>
       </c>
       <c r="K17" s="16" t="s">
         <v>49</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="M17" s="16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="13">
-        <v>46264</v>
+        <v>46263</v>
       </c>
       <c r="B18" s="14">
         <v>460</v>
@@ -1575,10 +1576,10 @@
         <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="E18" s="14">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="F18" s="14">
         <v>0</v>
@@ -1587,178 +1588,290 @@
         <v>0</v>
       </c>
       <c r="H18" s="14">
-        <v>310</v>
+        <v>253</v>
       </c>
       <c r="I18" s="15">
-        <v>1200</v>
+        <v>1193</v>
       </c>
       <c r="J18" s="15">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="L18" s="16" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="M18" s="16" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="13">
-        <v>46265</v>
+        <v>46264</v>
       </c>
       <c r="B19" s="14">
-        <v>420</v>
+        <v>460</v>
       </c>
       <c r="C19" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D19" s="14">
-        <v>410</v>
+        <v>230</v>
       </c>
       <c r="E19" s="14">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="F19" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G19" s="14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H19" s="14">
-        <v>375</v>
+        <v>310</v>
       </c>
       <c r="I19" s="15">
-        <v>1435</v>
+        <v>1200</v>
       </c>
       <c r="J19" s="15">
-        <v>5</v>
+        <v>240</v>
       </c>
       <c r="K19" s="16" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="M19" s="16" t="s">
         <v>57</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="13">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B20" s="14">
         <v>420</v>
       </c>
       <c r="C20" s="14">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D20" s="14">
-        <v>200</v>
+        <v>410</v>
       </c>
       <c r="E20" s="14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F20" s="14">
-        <v>350</v>
+        <v>100</v>
       </c>
       <c r="G20" s="14">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H20" s="14">
-        <v>200</v>
+        <v>375</v>
       </c>
       <c r="I20" s="15">
-        <v>1330</v>
+        <v>1435</v>
       </c>
       <c r="J20" s="15">
-        <v>110</v>
+        <v>5</v>
       </c>
       <c r="K20" s="16" t="s">
         <v>49</v>
       </c>
       <c r="L20" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A21" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B21" s="14">
+        <v>420</v>
+      </c>
+      <c r="C21" s="14">
+        <v>40</v>
+      </c>
+      <c r="D21" s="14">
+        <v>200</v>
+      </c>
+      <c r="E21" s="14">
+        <v>120</v>
+      </c>
+      <c r="F21" s="14">
+        <v>350</v>
+      </c>
+      <c r="G21" s="14">
+        <v>7</v>
+      </c>
+      <c r="H21" s="14">
+        <v>200</v>
+      </c>
+      <c r="I21" s="15">
+        <v>1330</v>
+      </c>
+      <c r="J21" s="15">
+        <v>110</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L21" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M20" s="16" t="s">
+      <c r="M21" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="N20" s="17" t="s">
+      <c r="N21" s="17" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15"/>
-      <c r="J21" s="15"/>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
-    </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15"/>
-      <c r="J22" s="15"/>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+      <c r="A22" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B22" s="14">
+        <v>420</v>
+      </c>
+      <c r="C22" s="14">
+        <v>20</v>
+      </c>
+      <c r="D22" s="14">
+        <v>240</v>
+      </c>
+      <c r="E22" s="14">
+        <v>130</v>
+      </c>
+      <c r="F22" s="14">
+        <v>200</v>
+      </c>
+      <c r="G22" s="14">
+        <v>4</v>
+      </c>
+      <c r="H22" s="14">
+        <v>250</v>
+      </c>
+      <c r="I22" s="15">
+        <v>1260</v>
+      </c>
+      <c r="J22" s="15">
+        <v>180</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15"/>
-      <c r="J23" s="15"/>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+      <c r="A23" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B23" s="14">
+        <v>400</v>
+      </c>
+      <c r="C23" s="14">
+        <v>30</v>
+      </c>
+      <c r="D23" s="14">
+        <v>150</v>
+      </c>
+      <c r="E23" s="14">
+        <v>120</v>
+      </c>
+      <c r="F23" s="14">
+        <v>350</v>
+      </c>
+      <c r="G23" s="14">
+        <v>7</v>
+      </c>
+      <c r="H23" s="14">
+        <v>200</v>
+      </c>
+      <c r="I23" s="15">
+        <v>1250</v>
+      </c>
+      <c r="J23" s="15">
+        <v>190</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15"/>
-      <c r="J24" s="15"/>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+      <c r="A24" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B24" s="14">
+        <v>430</v>
+      </c>
+      <c r="C24" s="14">
+        <v>40</v>
+      </c>
+      <c r="D24" s="14">
+        <v>140</v>
+      </c>
+      <c r="E24" s="14">
+        <v>90</v>
+      </c>
+      <c r="F24" s="14">
+        <v>350</v>
+      </c>
+      <c r="G24" s="14">
+        <v>7</v>
+      </c>
+      <c r="H24" s="14">
+        <v>340</v>
+      </c>
+      <c r="I24" s="15">
+        <v>1390</v>
+      </c>
+      <c r="J24" s="15">
+        <v>50</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>

--- a/12603423.xlsx
+++ b/12603423.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c73cdbbdc1b295c5/Desktop/excel for python/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="251" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{349ABAB0-2ED0-41D5-89C9-C215DED6558D}"/>
+  <xr:revisionPtr revIDLastSave="255" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{474AFC9C-1B2F-4E1F-8187-A313E2C3191F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -252,6 +252,9 @@
   <si>
     <t>Good day</t>
   </si>
+  <si>
+    <t>to day learn git&amp;github</t>
+  </si>
 </sst>
 </file>
 
@@ -433,10 +436,10 @@
     <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -924,74 +927,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="21">
+      <c r="F2" s="22">
         <v>12603423</v>
       </c>
-      <c r="G2" s="21"/>
+      <c r="G2" s="22"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="G3" s="21"/>
+      <c r="G3" s="22"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="19"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
     </row>
     <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
@@ -1082,8 +1085,8 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="22">
-        <v>46252</v>
+      <c r="A7" s="19">
+        <v>46253</v>
       </c>
       <c r="B7" s="14">
         <v>420</v>
@@ -1092,25 +1095,25 @@
         <v>30</v>
       </c>
       <c r="D7" s="14">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="E7" s="14">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="F7" s="14">
-        <v>540</v>
+        <v>240</v>
       </c>
       <c r="G7" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H7" s="14">
-        <v>195</v>
+        <v>300</v>
       </c>
       <c r="I7" s="15">
-        <v>1425</v>
+        <v>1440</v>
       </c>
       <c r="J7" s="15">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K7" s="16" t="s">
         <v>49</v>
@@ -1119,33 +1122,33 @@
         <v>50</v>
       </c>
       <c r="M7" s="16" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="N7" s="17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="13">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B8" s="14">
-        <v>420</v>
+        <v>450</v>
       </c>
       <c r="C8" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D8" s="14">
+        <v>280</v>
+      </c>
+      <c r="E8" s="14">
+        <v>90</v>
+      </c>
+      <c r="F8" s="14">
         <v>300</v>
       </c>
-      <c r="E8" s="14">
-        <v>150</v>
-      </c>
-      <c r="F8" s="14">
-        <v>240</v>
-      </c>
       <c r="G8" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H8" s="14">
         <v>300</v>
@@ -1157,42 +1160,42 @@
         <v>0</v>
       </c>
       <c r="K8" s="16" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="L8" s="16" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="M8" s="16" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="N8" s="18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="13">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B9" s="14">
-        <v>450</v>
+        <v>430</v>
       </c>
       <c r="C9" s="14">
         <v>20</v>
       </c>
       <c r="D9" s="14">
-        <v>280</v>
+        <v>140</v>
       </c>
       <c r="E9" s="14">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="F9" s="14">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="G9" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H9" s="14">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="I9" s="15">
         <v>1440</v>
@@ -1201,42 +1204,42 @@
         <v>0</v>
       </c>
       <c r="K9" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="L9" s="16" t="s">
-        <v>59</v>
-      </c>
       <c r="M9" s="16" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="13">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B10" s="14">
-        <v>430</v>
+        <v>460</v>
       </c>
       <c r="C10" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D10" s="14">
-        <v>140</v>
+        <v>300</v>
       </c>
       <c r="E10" s="14">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="F10" s="14">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G10" s="14">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H10" s="14">
-        <v>310</v>
+        <v>490</v>
       </c>
       <c r="I10" s="15">
         <v>1440</v>
@@ -1245,33 +1248,33 @@
         <v>0</v>
       </c>
       <c r="K10" s="16" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="L10" s="16" t="s">
         <v>56</v>
       </c>
       <c r="M10" s="16" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="13">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B11" s="14">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="C11" s="14">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D11" s="14">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="E11" s="14">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="F11" s="14">
         <v>0</v>
@@ -1280,7 +1283,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="14">
-        <v>490</v>
+        <v>410</v>
       </c>
       <c r="I11" s="15">
         <v>1440</v>
@@ -1289,285 +1292,285 @@
         <v>0</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="L11" s="16" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="M11" s="16" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="13">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B12" s="14">
-        <v>450</v>
+        <v>420</v>
       </c>
       <c r="C12" s="14">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D12" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="E12" s="14">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="F12" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G12" s="14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12" s="14">
-        <v>410</v>
+        <v>330</v>
       </c>
       <c r="I12" s="15">
-        <v>1440</v>
+        <v>1430</v>
       </c>
       <c r="J12" s="15">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K12" s="16" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L12" s="16" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="M12" s="16" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="13">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B13" s="14">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="C13" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D13" s="14">
-        <v>420</v>
+        <v>160</v>
       </c>
       <c r="E13" s="14">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="F13" s="14">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="G13" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H13" s="14">
-        <v>330</v>
+        <v>200</v>
       </c>
       <c r="I13" s="15">
-        <v>1430</v>
+        <v>1360</v>
       </c>
       <c r="J13" s="15">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="K13" s="16" t="s">
         <v>56</v>
       </c>
       <c r="L13" s="16" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M13" s="16" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="13">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B14" s="14">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="C14" s="13">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D14" s="14">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="E14" s="14">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="F14" s="14">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="G14" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H14" s="14">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I14" s="15">
-        <v>1360</v>
+        <v>1180</v>
       </c>
       <c r="J14" s="15">
-        <v>80</v>
+        <v>260</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="L14" s="16" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="M14" s="16" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="N14" s="17" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="13">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B15" s="14">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="C15" s="14">
         <v>20</v>
       </c>
       <c r="D15" s="14">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="E15" s="14">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="F15" s="14">
+        <v>350</v>
+      </c>
+      <c r="G15" s="14">
+        <v>7</v>
+      </c>
+      <c r="H15" s="14">
         <v>200</v>
       </c>
-      <c r="G15" s="14">
-        <v>4</v>
-      </c>
-      <c r="H15" s="14">
-        <v>300</v>
-      </c>
       <c r="I15" s="15">
-        <v>1180</v>
+        <v>1250</v>
       </c>
       <c r="J15" s="15">
-        <v>260</v>
+        <v>190</v>
       </c>
       <c r="K15" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N15" s="17" t="s">
         <v>49</v>
-      </c>
-      <c r="L15" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="M15" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="N15" s="17" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="13">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B16" s="14">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="C16" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D16" s="14">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="E16" s="14">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="F16" s="14">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="G16" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H16" s="14">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="I16" s="15">
-        <v>1250</v>
+        <v>1280</v>
       </c>
       <c r="J16" s="15">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="M16" s="16" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="13">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B17" s="14">
-        <v>420</v>
+        <v>460</v>
       </c>
       <c r="C17" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D17" s="14">
-        <v>130</v>
+        <v>250</v>
       </c>
       <c r="E17" s="14">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="F17" s="14">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G17" s="14">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H17" s="14">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="I17" s="15">
-        <v>1280</v>
+        <v>1193</v>
       </c>
       <c r="J17" s="15">
-        <v>160</v>
+        <v>247</v>
       </c>
       <c r="K17" s="16" t="s">
         <v>49</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="M17" s="16" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="13">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B18" s="14">
         <v>460</v>
@@ -1576,10 +1579,10 @@
         <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="E18" s="14">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="F18" s="14">
         <v>0</v>
@@ -1588,218 +1591,218 @@
         <v>0</v>
       </c>
       <c r="H18" s="14">
-        <v>253</v>
+        <v>310</v>
       </c>
       <c r="I18" s="15">
-        <v>1193</v>
+        <v>1200</v>
       </c>
       <c r="J18" s="15">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="L18" s="16" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="M18" s="16" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="13">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B19" s="14">
-        <v>460</v>
+        <v>420</v>
       </c>
       <c r="C19" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D19" s="14">
-        <v>230</v>
+        <v>410</v>
       </c>
       <c r="E19" s="14">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="F19" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G19" s="14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H19" s="14">
-        <v>310</v>
+        <v>375</v>
       </c>
       <c r="I19" s="15">
-        <v>1200</v>
+        <v>1435</v>
       </c>
       <c r="J19" s="15">
-        <v>240</v>
+        <v>5</v>
       </c>
       <c r="K19" s="16" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="M19" s="16" t="s">
         <v>57</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="13">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B20" s="14">
         <v>420</v>
       </c>
       <c r="C20" s="14">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D20" s="14">
-        <v>410</v>
+        <v>200</v>
       </c>
       <c r="E20" s="14">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="F20" s="14">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="G20" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H20" s="14">
-        <v>375</v>
+        <v>200</v>
       </c>
       <c r="I20" s="15">
-        <v>1435</v>
+        <v>1330</v>
       </c>
       <c r="J20" s="15">
-        <v>5</v>
+        <v>110</v>
       </c>
       <c r="K20" s="16" t="s">
         <v>49</v>
       </c>
       <c r="L20" s="16" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="M20" s="16" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="13">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B21" s="14">
         <v>420</v>
       </c>
       <c r="C21" s="14">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D21" s="14">
+        <v>240</v>
+      </c>
+      <c r="E21" s="14">
+        <v>130</v>
+      </c>
+      <c r="F21" s="14">
         <v>200</v>
       </c>
-      <c r="E21" s="14">
-        <v>120</v>
-      </c>
-      <c r="F21" s="14">
-        <v>350</v>
-      </c>
       <c r="G21" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H21" s="14">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="I21" s="15">
-        <v>1330</v>
+        <v>1260</v>
       </c>
       <c r="J21" s="15">
-        <v>110</v>
+        <v>180</v>
       </c>
       <c r="K21" s="16" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="L21" s="16" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="M21" s="16" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="N21" s="17" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="13">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B22" s="14">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="C22" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D22" s="14">
-        <v>240</v>
+        <v>150</v>
       </c>
       <c r="E22" s="14">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="F22" s="14">
+        <v>350</v>
+      </c>
+      <c r="G22" s="14">
+        <v>7</v>
+      </c>
+      <c r="H22" s="14">
         <v>200</v>
       </c>
-      <c r="G22" s="14">
-        <v>4</v>
-      </c>
-      <c r="H22" s="14">
-        <v>250</v>
-      </c>
       <c r="I22" s="15">
-        <v>1260</v>
+        <v>1250</v>
       </c>
       <c r="J22" s="15">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="K22" s="16" t="s">
         <v>56</v>
       </c>
       <c r="L22" s="16" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M22" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N22" s="17" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="13">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B23" s="14">
-        <v>400</v>
+        <v>430</v>
       </c>
       <c r="C23" s="14">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D23" s="14">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="E23" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="F23" s="14">
         <v>350</v>
@@ -1808,22 +1811,22 @@
         <v>7</v>
       </c>
       <c r="H23" s="14">
-        <v>200</v>
+        <v>340</v>
       </c>
       <c r="I23" s="15">
-        <v>1250</v>
+        <v>1390</v>
       </c>
       <c r="J23" s="15">
-        <v>190</v>
+        <v>50</v>
       </c>
       <c r="K23" s="16" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="L23" s="16" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="M23" s="16" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="N23" s="17" t="s">
         <v>64</v>
@@ -1831,143 +1834,311 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="13">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B24" s="14">
-        <v>430</v>
+        <v>460</v>
       </c>
       <c r="C24" s="14">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D24" s="14">
-        <v>140</v>
+        <v>250</v>
       </c>
       <c r="E24" s="14">
-        <v>90</v>
+        <v>210</v>
       </c>
       <c r="F24" s="14">
-        <v>350</v>
+        <v>100</v>
       </c>
       <c r="G24" s="14">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H24" s="14">
-        <v>340</v>
+        <v>253</v>
       </c>
       <c r="I24" s="15">
-        <v>1390</v>
+        <v>1293</v>
       </c>
       <c r="J24" s="15">
-        <v>50</v>
+        <v>147</v>
       </c>
       <c r="K24" s="16" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="L24" s="16" t="s">
         <v>59</v>
       </c>
       <c r="M24" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A25" s="13">
+        <v>46240</v>
+      </c>
+      <c r="B25" s="14">
+        <v>460</v>
+      </c>
+      <c r="C25" s="14">
+        <v>20</v>
+      </c>
+      <c r="D25" s="14">
+        <v>230</v>
+      </c>
+      <c r="E25" s="14">
+        <v>180</v>
+      </c>
+      <c r="F25" s="14">
+        <v>0</v>
+      </c>
+      <c r="G25" s="14">
+        <v>0</v>
+      </c>
+      <c r="H25" s="14">
+        <v>310</v>
+      </c>
+      <c r="I25" s="15">
+        <v>1200</v>
+      </c>
+      <c r="J25" s="15">
+        <v>240</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M25" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N24" s="17" t="s">
+      <c r="N25" s="17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A26" s="13">
+        <v>46241</v>
+      </c>
+      <c r="B26" s="14">
+        <v>460</v>
+      </c>
+      <c r="C26" s="14">
+        <v>20</v>
+      </c>
+      <c r="D26" s="14">
+        <v>230</v>
+      </c>
+      <c r="E26" s="14">
+        <v>180</v>
+      </c>
+      <c r="F26" s="14">
+        <v>90</v>
+      </c>
+      <c r="G26" s="14">
+        <v>3</v>
+      </c>
+      <c r="H26" s="14">
+        <v>310</v>
+      </c>
+      <c r="I26" s="15">
+        <v>1290</v>
+      </c>
+      <c r="J26" s="15">
+        <v>150</v>
+      </c>
+      <c r="K26" s="16" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15"/>
-      <c r="J25" s="15"/>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15"/>
-      <c r="J26" s="15"/>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+      <c r="L26" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15"/>
-      <c r="J27" s="15"/>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+      <c r="A27" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B27" s="14">
+        <v>400</v>
+      </c>
+      <c r="C27" s="14">
+        <v>30</v>
+      </c>
+      <c r="D27" s="14">
+        <v>150</v>
+      </c>
+      <c r="E27" s="14">
+        <v>120</v>
+      </c>
+      <c r="F27" s="14">
+        <v>350</v>
+      </c>
+      <c r="G27" s="14">
+        <v>7</v>
+      </c>
+      <c r="H27" s="14">
+        <v>200</v>
+      </c>
+      <c r="I27" s="15">
+        <v>1250</v>
+      </c>
+      <c r="J27" s="15">
+        <v>190</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15"/>
-      <c r="J28" s="15"/>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+      <c r="A28" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B28" s="14">
+        <v>420</v>
+      </c>
+      <c r="C28" s="14">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
+        <v>240</v>
+      </c>
+      <c r="E28" s="14">
+        <v>130</v>
+      </c>
+      <c r="F28" s="14">
+        <v>200</v>
+      </c>
+      <c r="G28" s="14">
+        <v>4</v>
+      </c>
+      <c r="H28" s="14">
+        <v>250</v>
+      </c>
+      <c r="I28" s="15">
+        <v>1260</v>
+      </c>
+      <c r="J28" s="15">
+        <v>180</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15"/>
-      <c r="J29" s="15"/>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+      <c r="A29" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B29" s="14">
+        <v>430</v>
+      </c>
+      <c r="C29" s="14">
+        <v>30</v>
+      </c>
+      <c r="D29" s="14">
+        <v>180</v>
+      </c>
+      <c r="E29" s="14">
+        <v>120</v>
+      </c>
+      <c r="F29" s="14">
+        <v>350</v>
+      </c>
+      <c r="G29" s="14">
+        <v>7</v>
+      </c>
+      <c r="H29" s="14">
+        <v>220</v>
+      </c>
+      <c r="I29" s="15">
+        <v>1330</v>
+      </c>
+      <c r="J29" s="15">
+        <v>110</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="15"/>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+      <c r="A30" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B30" s="14">
+        <v>450</v>
+      </c>
+      <c r="C30" s="14">
+        <v>30</v>
+      </c>
+      <c r="D30" s="14">
+        <v>170</v>
+      </c>
+      <c r="E30" s="14">
+        <v>120</v>
+      </c>
+      <c r="F30" s="14">
+        <v>350</v>
+      </c>
+      <c r="G30" s="14">
+        <v>7</v>
+      </c>
+      <c r="H30" s="14">
+        <v>300</v>
+      </c>
+      <c r="I30" s="15">
+        <v>1420</v>
+      </c>
+      <c r="J30" s="15">
+        <v>20</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="13"/>
@@ -2235,11 +2406,11 @@
       <c r="G47" s="14"/>
       <c r="H47" s="14"/>
       <c r="I47" s="15" t="str">
-        <f t="shared" ref="I6:I69" si="0">IF(SUM(B47:F47,H47)=0,"",SUM(B47:F47,H47))</f>
+        <f t="shared" ref="I47:I69" si="0">IF(SUM(B47:F47,H47)=0,"",SUM(B47:F47,H47))</f>
         <v/>
       </c>
       <c r="J47" s="15" t="str">
-        <f t="shared" ref="J6:J69" si="1">IF(I47="","",1440-I47)</f>
+        <f t="shared" ref="J47:J69" si="1">IF(I47="","",1440-I47)</f>
         <v/>
       </c>
       <c r="K47" s="16"/>
